--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,6 +1051,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129405494</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557363</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6632093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,6 +1166,253 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129432707</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557303</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6632079</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129436946</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557271</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6632079</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129432707</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129436946</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129432707</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129436946</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129432707</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129436946</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>129405494</v>
       </c>
       <c r="B5" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>129432707</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129436946</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>129432707</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>129436946</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>132142335</v>
       </c>
       <c r="B9" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>79890642</v>
       </c>
       <c r="B2" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557331.9051950271</v>
+        <v>557332</v>
       </c>
       <c r="R2" t="n">
-        <v>6632164.347937653</v>
+        <v>6632164</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -751,19 +746,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,56 +786,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79890426</v>
+        <v>129405494</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sylbergen V, Vstm</t>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557331.9051950271</v>
+        <v>557363</v>
       </c>
       <c r="R3" t="n">
-        <v>6632164.347937653</v>
+        <v>6632093</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,44 +884,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79889454</v>
+        <v>79890426</v>
       </c>
       <c r="B4" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557331.9051950271</v>
+        <v>557332</v>
       </c>
       <c r="R4" t="n">
-        <v>6632164.347937653</v>
+        <v>6632164</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -1003,19 +973,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129405494</v>
+        <v>132142335</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,43 +1024,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557363</v>
+        <v>557419</v>
       </c>
       <c r="R5" t="n">
-        <v>6632093</v>
+        <v>6632197</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,22 +1081,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,80 +1110,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sören Larsson, Pia Hagfors, Thomas Janzon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129432707</v>
+        <v>79889454</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen V, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557303</v>
+        <v>557332</v>
       </c>
       <c r="R6" t="n">
-        <v>6632079</v>
+        <v>6632164</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,22 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2019-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2019-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,55 +1215,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129436946</v>
+        <v>126885437</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1328,24 +1282,34 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+          <t>Målsjövägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557271</v>
+        <v>557276</v>
       </c>
       <c r="R7" t="n">
-        <v>6632079</v>
+        <v>6632060</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1333,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,11 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1409,17 +1368,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Solveig Hagfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132142239</v>
+        <v>132142130</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1403,11 @@
           <t>Paykull, 1800</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1460,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557422</v>
+        <v>557322</v>
       </c>
       <c r="R8" t="n">
-        <v>6632055</v>
+        <v>6632054</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1510,7 +1473,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På barkfri gran.</t>
+          <t>På liggande barkfri gran. Även flera gnagspår efter bråbndad barlbock på samma träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132142335</v>
+        <v>132142239</v>
       </c>
       <c r="B9" t="n">
-        <v>91876</v>
+        <v>5181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,26 +1516,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1580,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557419</v>
+        <v>557422</v>
       </c>
       <c r="R9" t="n">
-        <v>6632197</v>
+        <v>6632055</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1630,7 +1599,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På barkfri gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,6 +1628,381 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129566258</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557265</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6632060</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-03-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-03-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tupp sprang på snön på vägen och spelade.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129432707</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557303</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6632079</v>
+      </c>
+      <c r="S11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129436946</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Målsjövägen, Ramnäs, Vstm, Målsjövägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557271</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6632079</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -2181,7 +2181,11 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79890642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129405494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79890426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142335</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79889454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126885437</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142130</t>
         </is>
       </c>
     </row>
@@ -1628,6 +1668,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142239</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1756,6 +1801,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129566258</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1877,6 +1927,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129432707</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2003,6 +2058,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129436946</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2142,6 +2202,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134863096</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2281,6 +2346,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134863137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2420,8 +2490,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134863080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>134863137</v>
       </c>
       <c r="B14" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134863080</v>
+        <v>134863137</v>
       </c>
       <c r="B14" t="n">
-        <v>56856</v>
+        <v>56838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,26 +2221,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2250,7 +2246,11 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -2292,22 +2292,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>02:51</t>
+          <t>00:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>02:34</t>
+          <t>00:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>öppen glänta vid sumpskog</t>
+          <t>Öppen glänta invid sumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2347,6 +2347,150 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134863137</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134863080</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56856</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557272</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6632108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>öppen glänta vid sumpskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134863080</t>
         </is>
@@ -2367,6 +2511,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39594-2025 artfynd.xlsx
+++ b/artfynd/A 39594-2025 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>134863137</v>
       </c>
       <c r="B14" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
